--- a/frontend/public/bulk_import_templates/bulk_import_template.xlsx
+++ b/frontend/public/bulk_import_templates/bulk_import_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smith/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zeffmorgan/src/lyrasis/archivesspace/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47507471-0CA2-B349-A936-7EE5FB8532AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D71783-F4B3-4846-9F94-907FE5F5F64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="9140" windowWidth="27040" windowHeight="16860" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34560" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="501">
   <si>
     <t>This is the template for importing archival objects using the bulk_import ("Load SpreadSheet").  You may replace this line with something of your choosing after you've copied the file for your use.</t>
   </si>
@@ -207,6 +207,69 @@
 (Note that Publish value will be inherited by each File Version in addition to being set on the Digital Object record. Leave this blank to get the default value FALSE.)</t>
   </si>
   <si>
+    <t>Linked-to URL for representative file version</t>
+  </si>
+  <si>
+    <t>Use Statement for representative file version</t>
+  </si>
+  <si>
+    <t>Xlink actuate attribute for representative file version (previous default 'onRequest')</t>
+  </si>
+  <si>
+    <t>Xlink show attribute for representative file version (previous default 'new')</t>
+  </si>
+  <si>
+    <t>File Format Name for representative file version</t>
+  </si>
+  <si>
+    <t>File Format Version for representative file version</t>
+  </si>
+  <si>
+    <t>File size (bytes) for representative file version</t>
+  </si>
+  <si>
+    <t>Checksum for representative file version</t>
+  </si>
+  <si>
+    <t>Checksum Method for representative file version</t>
+  </si>
+  <si>
+    <t>Caption for representative file version</t>
+  </si>
+  <si>
+    <t>Linked-to URL for non-representative file version</t>
+  </si>
+  <si>
+    <t>Publish non-representative file version?</t>
+  </si>
+  <si>
+    <t>Use Statement for non-representative file version</t>
+  </si>
+  <si>
+    <t>Xlink actuate attribute for non-representative file version (previous default 'onLoad')</t>
+  </si>
+  <si>
+    <t>Xlink show attribute for non-representative file version (previous default 'embed')</t>
+  </si>
+  <si>
+    <t>File Format Name for non-representative file version</t>
+  </si>
+  <si>
+    <t>File Format Version for non-representative file version</t>
+  </si>
+  <si>
+    <t>File size (bytes) for non-representative file version</t>
+  </si>
+  <si>
+    <t>Checksum for non-representative file version</t>
+  </si>
+  <si>
+    <t>Checksum Method for non-representative file version</t>
+  </si>
+  <si>
+    <t>Caption for non-representative file version</t>
+  </si>
+  <si>
     <t>Person Agent Record ID
 (The numeric suffix on the URL of the Agent record, e.g., 9921 for  https://arstaffqa.hul.harvard.edu/agents/agent_person/9921</t>
   </si>
@@ -618,6 +681,69 @@
     <t>digital_object_publish</t>
   </si>
   <si>
+    <t>rep_file_uri</t>
+  </si>
+  <si>
+    <t>rep_use_statement</t>
+  </si>
+  <si>
+    <t>rep_xlink_actuate_attribute</t>
+  </si>
+  <si>
+    <t>rep_xlink_show_attribute</t>
+  </si>
+  <si>
+    <t>rep_file_format</t>
+  </si>
+  <si>
+    <t>rep_file_format_version</t>
+  </si>
+  <si>
+    <t>rep_file_size</t>
+  </si>
+  <si>
+    <t>rep_checksum</t>
+  </si>
+  <si>
+    <t>rep_checksum_method</t>
+  </si>
+  <si>
+    <t>rep_caption</t>
+  </si>
+  <si>
+    <t>nonrep_file_uri</t>
+  </si>
+  <si>
+    <t>nonrep_publish</t>
+  </si>
+  <si>
+    <t>nonrep_use_statement</t>
+  </si>
+  <si>
+    <t>nonrep_xlink_actuate_attribute</t>
+  </si>
+  <si>
+    <t>nonrep_xlink_show_attribute</t>
+  </si>
+  <si>
+    <t>nonrep_file_format</t>
+  </si>
+  <si>
+    <t>nonrep_file_format_version</t>
+  </si>
+  <si>
+    <t>nonrep_file_size</t>
+  </si>
+  <si>
+    <t>nonrep_checksum</t>
+  </si>
+  <si>
+    <t>nonrep_checksum_method</t>
+  </si>
+  <si>
+    <t>nonrep_caption</t>
+  </si>
+  <si>
     <t>people_agent_record_id_1</t>
   </si>
   <si>
@@ -786,9 +912,6 @@
     <t>e_accessrestrict</t>
   </si>
   <si>
-    <t>t_accessrestrict</t>
-  </si>
-  <si>
     <t>n_acqinfo</t>
   </si>
   <si>
@@ -1095,6 +1218,39 @@
     <t>Publish Digital Object Record</t>
   </si>
   <si>
+    <t>URL of representative file version</t>
+  </si>
+  <si>
+    <t>Use Statement</t>
+  </si>
+  <si>
+    <t>xlink actuate attribute</t>
+  </si>
+  <si>
+    <t>xlink show attribute</t>
+  </si>
+  <si>
+    <t>File Format Name</t>
+  </si>
+  <si>
+    <t>File Format Version</t>
+  </si>
+  <si>
+    <t>File Size</t>
+  </si>
+  <si>
+    <t>Checksum</t>
+  </si>
+  <si>
+    <t>Checksum Method</t>
+  </si>
+  <si>
+    <t>Caption</t>
+  </si>
+  <si>
+    <t>URL of non-representative file version</t>
+  </si>
+  <si>
     <t>Publish</t>
   </si>
   <si>
@@ -1380,163 +1536,10 @@
     <t>Subject</t>
   </si>
   <si>
-    <t>Linked-to URL for representative file version</t>
-  </si>
-  <si>
-    <t>URL of representative file version</t>
-  </si>
-  <si>
-    <t>rep_xlink_actuate_attribute</t>
-  </si>
-  <si>
-    <t>rep_xlink_show_attribute</t>
-  </si>
-  <si>
-    <t>xlink actuate attribute</t>
-  </si>
-  <si>
-    <t>xlink show attribute</t>
-  </si>
-  <si>
-    <t>Linked-to URL for non-representative file version</t>
-  </si>
-  <si>
-    <t>Publish non-representative file version?</t>
-  </si>
-  <si>
-    <t>nonrep_xlink_actuate_attribute</t>
-  </si>
-  <si>
-    <t>nonrep_xlink_show_attribute</t>
-  </si>
-  <si>
-    <t>URL of non-representative file version</t>
-  </si>
-  <si>
-    <t>Xlink show attribute for non-representative file version (previous default 'embed')</t>
-  </si>
-  <si>
-    <t>Xlink actuate attribute for non-representative file version (previous default 'onLoad')</t>
-  </si>
-  <si>
-    <t>Xlink show attribute for representative file version (previous default 'new')</t>
-  </si>
-  <si>
-    <t>Xlink actuate attribute for representative file version (previous default 'onRequest')</t>
-  </si>
-  <si>
-    <t>rep_use_statement</t>
-  </si>
-  <si>
-    <t>rep_file_format</t>
-  </si>
-  <si>
-    <t>rep_file_format_version</t>
-  </si>
-  <si>
-    <t>rep_file_size</t>
-  </si>
-  <si>
-    <t>Use Statement</t>
-  </si>
-  <si>
-    <t>File Format Name</t>
-  </si>
-  <si>
-    <t>File Format Version</t>
-  </si>
-  <si>
-    <t>Checksum</t>
-  </si>
-  <si>
-    <t>rep_checksum</t>
-  </si>
-  <si>
-    <t>Checksum Method</t>
-  </si>
-  <si>
-    <t>rep_checksum_method</t>
-  </si>
-  <si>
-    <t>Caption</t>
-  </si>
-  <si>
-    <t>rep_caption</t>
-  </si>
-  <si>
-    <t>Use Statement for representative file version</t>
-  </si>
-  <si>
-    <t>File Format Name for representative file version</t>
-  </si>
-  <si>
-    <t>File Format Version for representative file version</t>
-  </si>
-  <si>
-    <t>File size (bytes) for representative file version</t>
-  </si>
-  <si>
-    <t>Checksum for representative file version</t>
-  </si>
-  <si>
-    <t>Checksum Method for representative file version</t>
-  </si>
-  <si>
-    <t>Caption for representative file version</t>
-  </si>
-  <si>
-    <t>Use Statement for non-representative file version</t>
-  </si>
-  <si>
-    <t>File Format Name for non-representative file version</t>
-  </si>
-  <si>
-    <t>File Format Version for non-representative file version</t>
-  </si>
-  <si>
-    <t>File size (bytes) for non-representative file version</t>
-  </si>
-  <si>
-    <t>Checksum for non-representative file version</t>
-  </si>
-  <si>
-    <t>Checksum Method for non-representative file version</t>
-  </si>
-  <si>
-    <t>Caption for non-representative file version</t>
-  </si>
-  <si>
-    <t>nonrep_use_statement</t>
-  </si>
-  <si>
-    <t>nonrep_file_format</t>
-  </si>
-  <si>
-    <t>nonrep_file_format_version</t>
-  </si>
-  <si>
-    <t>nonrep_file_size</t>
-  </si>
-  <si>
-    <t>nonrep_checksum</t>
-  </si>
-  <si>
-    <t>nonrep_checksum_method</t>
-  </si>
-  <si>
-    <t>nonrep_caption</t>
-  </si>
-  <si>
-    <t>File Size</t>
-  </si>
-  <si>
-    <t>nonrep_publish</t>
-  </si>
-  <si>
-    <t>nonrep_file_uri</t>
-  </si>
-  <si>
-    <t>rep_file_uri</t>
+    <t>t_accessrestrict_1</t>
+  </si>
+  <si>
+    <t>Access Restrictions Type(1)</t>
   </si>
 </sst>
 </file>
@@ -1618,17 +1621,17 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1777,7 +1780,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1936,8 +1939,8 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1969,7 +1972,7 @@
       <rgbColor rgb="FFDCE6F2"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFD99694"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF0563C1"/>
       <rgbColor rgb="FFC6D9F1"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -2044,39 +2047,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -2128,7 +2131,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2239,13 +2242,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -2254,6 +2250,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2318,11 +2321,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2330,7 +2353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:ANA1005"/>
+  <dimension ref="A1:AMJ1005"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" style="1" customWidth="1"/>
@@ -2378,7 +2401,9 @@
     <col min="62" max="62" width="15.83203125" style="2" customWidth="1"/>
     <col min="63" max="63" width="10.5" style="2" customWidth="1"/>
     <col min="64" max="64" width="20.6640625" customWidth="1"/>
-    <col min="65" max="76" width="12" style="2" customWidth="1"/>
+    <col min="65" max="65" width="12" style="2" customWidth="1"/>
+    <col min="66" max="66" width="12" style="3" customWidth="1"/>
+    <col min="67" max="76" width="12" style="2" customWidth="1"/>
     <col min="77" max="77" width="15.33203125" style="2" customWidth="1"/>
     <col min="78" max="79" width="12" style="2" customWidth="1"/>
     <col min="80" max="80" width="22.6640625" style="2" customWidth="1"/>
@@ -2470,10 +2495,10 @@
     <col min="178" max="178" width="10.1640625" style="2" customWidth="1"/>
     <col min="179" max="179" width="17.6640625" style="2" customWidth="1"/>
     <col min="180" max="180" width="17.6640625" customWidth="1"/>
-    <col min="181" max="1034" width="9.33203125" style="2"/>
+    <col min="181" max="1024" width="9.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1041" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:188" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2495,7 +2520,7 @@
       <c r="FU1" s="2"/>
       <c r="FX1" s="2"/>
     </row>
-    <row r="2" spans="1:1041" ht="61" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:188" ht="60" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -3057,15 +3082,8 @@
       <c r="GE2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="AMU2" s="2"/>
-      <c r="AMV2" s="2"/>
-      <c r="AMW2" s="2"/>
-      <c r="AMX2" s="2"/>
-      <c r="AMY2" s="2"/>
-      <c r="AMZ2" s="2"/>
-      <c r="ANA2" s="2"/>
-    </row>
-    <row r="3" spans="1:1041" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:188" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
         <v>15</v>
       </c>
@@ -3257,2533 +3275,1508 @@
         <v>57</v>
       </c>
       <c r="BM3" s="34" t="s">
-        <v>447</v>
+        <v>58</v>
       </c>
       <c r="BN3" s="34" t="s">
-        <v>475</v>
+        <v>59</v>
       </c>
       <c r="BO3" s="34" t="s">
-        <v>461</v>
+        <v>60</v>
       </c>
       <c r="BP3" s="34" t="s">
-        <v>460</v>
+        <v>61</v>
       </c>
       <c r="BQ3" s="34" t="s">
-        <v>476</v>
+        <v>62</v>
       </c>
       <c r="BR3" s="34" t="s">
-        <v>477</v>
+        <v>63</v>
       </c>
       <c r="BS3" s="34" t="s">
-        <v>478</v>
+        <v>64</v>
       </c>
       <c r="BT3" s="34" t="s">
-        <v>479</v>
+        <v>65</v>
       </c>
       <c r="BU3" s="34" t="s">
-        <v>480</v>
+        <v>66</v>
       </c>
       <c r="BV3" s="34" t="s">
-        <v>481</v>
+        <v>67</v>
       </c>
       <c r="BW3" s="34" t="s">
-        <v>453</v>
+        <v>68</v>
       </c>
       <c r="BX3" s="34" t="s">
-        <v>454</v>
+        <v>69</v>
       </c>
       <c r="BY3" s="34" t="s">
-        <v>482</v>
+        <v>70</v>
       </c>
       <c r="BZ3" s="34" t="s">
-        <v>459</v>
+        <v>71</v>
       </c>
       <c r="CA3" s="34" t="s">
-        <v>458</v>
+        <v>72</v>
       </c>
       <c r="CB3" s="34" t="s">
-        <v>483</v>
+        <v>73</v>
       </c>
       <c r="CC3" s="34" t="s">
-        <v>484</v>
+        <v>74</v>
       </c>
       <c r="CD3" s="34" t="s">
-        <v>485</v>
+        <v>75</v>
       </c>
       <c r="CE3" s="34" t="s">
-        <v>486</v>
+        <v>76</v>
       </c>
       <c r="CF3" s="34" t="s">
-        <v>487</v>
+        <v>77</v>
       </c>
       <c r="CG3" s="34" t="s">
-        <v>488</v>
+        <v>78</v>
       </c>
       <c r="CH3" s="35" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="CI3" s="35" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="CJ3" s="35" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="CK3" s="35" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="CL3" s="35" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="CM3" s="35" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="CN3" s="35" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="CO3" s="35" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="CP3" s="35" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="CQ3" s="35" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="CR3" s="35" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="CS3" s="35" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="CT3" s="35" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="CU3" s="35" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="CV3" s="35" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="CW3" s="35" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="CX3" s="35" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="CY3" s="35" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="CZ3" s="35" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="DA3" s="35" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="DB3" s="35" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="DC3" s="35" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="DD3" s="35" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="DE3" s="35" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="DF3" s="35" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="DG3" s="35" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="DH3" s="35" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="DI3" s="35" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="DJ3" s="35" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="DK3" s="35" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="DL3" s="35" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="DM3" s="35" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="DN3" s="35" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="DO3" s="35" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="DP3" s="35" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="DQ3" s="35" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="DR3" s="35" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="DS3" s="35" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="DT3" s="35" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="DU3" s="35" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="DV3" s="32" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="DW3" s="32" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="DX3" s="32" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="DY3" s="32" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="DZ3" s="32" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="EA3" s="32" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="EB3" s="32" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="EC3" s="32" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="ED3" s="36" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="EE3" s="36" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="EF3" s="36" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="EG3" s="36" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="EH3" s="36" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="EI3" s="36" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="EJ3" s="36" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="EK3" s="36" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="EL3" s="36" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="EM3" s="36" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="EN3" s="36" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="EO3" s="36" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="EP3" s="36" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="EQ3" s="36" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="ER3" s="36" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="ES3" s="36" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="ET3" s="36" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="EU3" s="36" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="EV3" s="36" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="EW3" s="36" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="EX3" s="36" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="EY3" s="36" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="EZ3" s="36" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="FA3" s="36" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="FB3" s="36" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="FC3" s="36" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="FD3" s="36" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="FE3" s="36" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="FF3" s="36" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="FG3" s="36" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="FH3" s="36" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="FI3" s="36" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="FJ3" s="36" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="FK3" s="36" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="FL3" s="36" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="FM3" s="36" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="FN3" s="36" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="FO3" s="36" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="FP3" s="36" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="FQ3" s="36" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="FR3" s="36" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="FS3" s="36" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="FT3" s="36" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="FU3" s="36" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="FV3" s="36" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="FW3" s="36" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="FX3" s="36" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="FY3" s="36" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="FZ3" s="36" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="GA3" s="36" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="GB3" s="36" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="GC3" s="36" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="GD3" s="36" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="GE3" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="AMU3" s="2"/>
-      <c r="AMV3" s="2"/>
-      <c r="AMW3" s="2"/>
-      <c r="AMX3" s="2"/>
-      <c r="AMY3" s="2"/>
-      <c r="AMZ3" s="2"/>
-      <c r="ANA3" s="2"/>
-    </row>
-    <row r="4" spans="1:1041" s="43" customFormat="1" ht="56.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:188" s="43" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="37" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="D4" s="38" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="I4" s="38" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="K4" s="38" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L4" s="41" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M4" s="38" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="N4" s="38" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="O4" s="38" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="P4" s="38" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="Q4" s="38" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="R4" s="38" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="S4" s="38" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="T4" s="38" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="U4" s="38" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="V4" s="38" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="W4" s="39" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="X4" s="39" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="Y4" s="38" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="Z4" s="39" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="AA4" s="38" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="AB4" s="38" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="AC4" s="39" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="AD4" s="39" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="AE4" s="38" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="AF4" s="39" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="AG4" s="38" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="AH4" s="38" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="AI4" s="38" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="AJ4" s="38" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="AK4" s="38" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="AL4" s="38" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="AM4" s="40" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="AN4" s="38" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="AO4" s="38" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="AP4" s="38" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="AQ4" s="38" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AR4" s="38" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="AS4" s="42" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="AT4" s="38" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="AU4" s="38" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="AV4" s="39" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="AW4" s="38" t="s">
         <v>50</v>
       </c>
       <c r="AX4" s="39" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="AY4" s="39" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="AZ4" s="38" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="BA4" s="39" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="BB4" s="38" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="BC4" s="38" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="BD4" s="39" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="BE4" s="38" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="BF4" s="39" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="BG4" s="39" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="BH4" s="38" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="BI4" s="39" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="BJ4" s="38" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="BK4" s="38" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="BL4" s="38" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="BM4" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="BN4" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="BO4" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="BP4" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="BQ4" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="BR4" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="BS4" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="BT4" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="BU4" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="BV4" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="BW4" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="BX4" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="BY4" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="BZ4" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="CA4" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="CB4" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="CC4" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="CD4" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="CE4" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="CF4" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="CG4" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="CH4" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="CI4" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="CJ4" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="CK4" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="CL4" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="CM4" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="CN4" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO4" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP4" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="CQ4" s="38" t="s">
+        <v>244</v>
+      </c>
+      <c r="CR4" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="CS4" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="CT4" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="CU4" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="CV4" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="CW4" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="CX4" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="CY4" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="CZ4" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="DA4" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="DB4" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="DC4" s="38" t="s">
+        <v>256</v>
+      </c>
+      <c r="DD4" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="DE4" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="DF4" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="DG4" s="38" t="s">
+        <v>260</v>
+      </c>
+      <c r="DH4" s="38" t="s">
+        <v>261</v>
+      </c>
+      <c r="DI4" s="38" t="s">
+        <v>262</v>
+      </c>
+      <c r="DJ4" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="DK4" s="38" t="s">
+        <v>264</v>
+      </c>
+      <c r="DL4" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="DM4" s="38" t="s">
+        <v>266</v>
+      </c>
+      <c r="DN4" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="DO4" s="38" t="s">
+        <v>268</v>
+      </c>
+      <c r="DP4" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="DQ4" s="38" t="s">
+        <v>270</v>
+      </c>
+      <c r="DR4" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="DS4" s="38" t="s">
+        <v>272</v>
+      </c>
+      <c r="DT4" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="DU4" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="DV4" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="DW4" s="38" t="s">
+        <v>276</v>
+      </c>
+      <c r="DX4" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="DY4" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="DZ4" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="EA4" s="38" t="s">
+        <v>280</v>
+      </c>
+      <c r="EB4" s="38" t="s">
+        <v>281</v>
+      </c>
+      <c r="EC4" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="ED4" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="EE4" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="EF4" s="38" t="s">
+        <v>285</v>
+      </c>
+      <c r="EG4" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="EH4" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="EI4" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="EJ4" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="EK4" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="EL4" s="38" t="s">
         <v>499</v>
       </c>
-      <c r="BN4" s="38" t="s">
-        <v>462</v>
-      </c>
-      <c r="BO4" s="38" t="s">
-        <v>449</v>
-      </c>
-      <c r="BP4" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="BQ4" s="38" t="s">
-        <v>463</v>
-      </c>
-      <c r="BR4" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="BS4" s="38" t="s">
-        <v>465</v>
-      </c>
-      <c r="BT4" s="38" t="s">
-        <v>470</v>
-      </c>
-      <c r="BU4" s="38" t="s">
-        <v>472</v>
-      </c>
-      <c r="BV4" s="38" t="s">
-        <v>474</v>
-      </c>
-      <c r="BW4" s="38" t="s">
-        <v>498</v>
-      </c>
-      <c r="BX4" s="38" t="s">
-        <v>497</v>
-      </c>
-      <c r="BY4" s="38" t="s">
-        <v>489</v>
-      </c>
-      <c r="BZ4" s="38" t="s">
-        <v>455</v>
-      </c>
-      <c r="CA4" s="38" t="s">
-        <v>456</v>
-      </c>
-      <c r="CB4" s="38" t="s">
-        <v>490</v>
-      </c>
-      <c r="CC4" s="38" t="s">
-        <v>491</v>
-      </c>
-      <c r="CD4" s="38" t="s">
-        <v>492</v>
-      </c>
-      <c r="CE4" s="38" t="s">
-        <v>493</v>
-      </c>
-      <c r="CF4" s="38" t="s">
-        <v>494</v>
-      </c>
-      <c r="CG4" s="38" t="s">
-        <v>495</v>
-      </c>
-      <c r="CH4" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="CI4" s="38" t="s">
-        <v>194</v>
-      </c>
-      <c r="CJ4" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="CK4" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="CL4" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="CM4" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="CN4" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="CO4" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="CP4" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="CQ4" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="CR4" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="CS4" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="CT4" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="CU4" s="38" t="s">
-        <v>206</v>
-      </c>
-      <c r="CV4" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="CW4" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="CX4" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="CY4" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="CZ4" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="DA4" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="DB4" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="DC4" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="DD4" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="DE4" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="DF4" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="DG4" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="DH4" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="DI4" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="DJ4" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="DK4" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="DL4" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="DM4" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="DN4" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="DO4" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="DP4" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="DQ4" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="DR4" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="DS4" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="DT4" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="DU4" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="DV4" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="DW4" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="DX4" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="DY4" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="DZ4" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="EA4" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="EB4" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="EC4" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="ED4" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="EE4" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="EF4" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="EG4" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="EH4" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="EI4" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="EJ4" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="EK4" s="38" t="s">
-        <v>248</v>
-      </c>
-      <c r="EL4" s="38" t="s">
-        <v>249</v>
-      </c>
       <c r="EM4" s="40" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="EN4" s="38" t="s">
-        <v>251</v>
+        <v>292</v>
       </c>
       <c r="EO4" s="38" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="EP4" s="38" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="EQ4" s="38" t="s">
-        <v>254</v>
+        <v>295</v>
       </c>
       <c r="ER4" s="38" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="ES4" s="38" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="ET4" s="38" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="EU4" s="38" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="EV4" s="38" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="EW4" s="38" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="EX4" s="38" t="s">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="EY4" s="38" t="s">
-        <v>262</v>
+        <v>303</v>
       </c>
       <c r="EZ4" s="38" t="s">
-        <v>263</v>
+        <v>304</v>
       </c>
       <c r="FA4" s="38" t="s">
-        <v>264</v>
+        <v>305</v>
       </c>
       <c r="FB4" s="38" t="s">
-        <v>265</v>
+        <v>306</v>
       </c>
       <c r="FC4" s="38" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="FD4" s="38" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="FE4" s="38" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="FF4" s="38" t="s">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="FG4" s="38" t="s">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="FH4" s="38" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="FI4" s="38" t="s">
-        <v>272</v>
+        <v>313</v>
       </c>
       <c r="FJ4" s="38" t="s">
-        <v>273</v>
+        <v>314</v>
       </c>
       <c r="FK4" s="38" t="s">
-        <v>274</v>
+        <v>315</v>
       </c>
       <c r="FL4" s="38" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="FM4" s="38" t="s">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="FN4" s="38" t="s">
-        <v>277</v>
+        <v>318</v>
       </c>
       <c r="FO4" s="38" t="s">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="FP4" s="38" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
       <c r="FQ4" s="38" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
       <c r="FR4" s="38" t="s">
-        <v>281</v>
+        <v>322</v>
       </c>
       <c r="FS4" s="38" t="s">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="FT4" s="38" t="s">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="FU4" s="38" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="FV4" s="38" t="s">
-        <v>285</v>
+        <v>326</v>
       </c>
       <c r="FW4" s="38" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="FX4" s="38" t="s">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="FY4" s="38" t="s">
-        <v>288</v>
+        <v>329</v>
       </c>
       <c r="FZ4" s="38" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="GA4" s="38" t="s">
-        <v>290</v>
+        <v>331</v>
       </c>
       <c r="GB4" s="38" t="s">
-        <v>291</v>
+        <v>332</v>
       </c>
       <c r="GC4" s="38" t="s">
-        <v>292</v>
+        <v>333</v>
       </c>
       <c r="GD4" s="38" t="s">
-        <v>293</v>
+        <v>334</v>
       </c>
       <c r="GE4" s="38" t="s">
-        <v>294</v>
+        <v>335</v>
       </c>
       <c r="GF4" s="2"/>
     </row>
-    <row r="5" spans="1:1041" ht="57.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:188" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="44" t="s">
-        <v>295</v>
+        <v>336</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>297</v>
+        <v>338</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>298</v>
+        <v>339</v>
       </c>
       <c r="E5" s="47" t="s">
-        <v>299</v>
+        <v>340</v>
       </c>
       <c r="F5" s="46" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="48" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="I5" s="46" t="s">
-        <v>302</v>
+        <v>343</v>
       </c>
       <c r="J5" s="47" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="K5" s="47" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="L5" s="49" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="M5" s="47" t="s">
-        <v>306</v>
+        <v>347</v>
       </c>
       <c r="N5" s="47" t="s">
         <v>5</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="P5" s="47" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="Q5" s="47" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="R5" s="47" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="S5" s="47" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="T5" s="47" t="s">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="U5" s="47" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="V5" s="47" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="W5" s="50" t="s">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="X5" s="50" t="s">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="Y5" s="46" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="Z5" s="50" t="s">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="AA5" s="47" t="s">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="AB5" s="47" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
       <c r="AC5" s="50" t="s">
-        <v>319</v>
+        <v>360</v>
       </c>
       <c r="AD5" s="50" t="s">
-        <v>320</v>
+        <v>361</v>
       </c>
       <c r="AE5" s="46" t="s">
-        <v>321</v>
+        <v>362</v>
       </c>
       <c r="AF5" s="50" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="AG5" s="47" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="AH5" s="47" t="s">
-        <v>324</v>
+        <v>365</v>
       </c>
       <c r="AI5" s="46" t="s">
         <v>42</v>
       </c>
       <c r="AJ5" s="46" t="s">
-        <v>325</v>
+        <v>366</v>
       </c>
       <c r="AK5" s="47" t="s">
         <v>44</v>
       </c>
       <c r="AL5" s="47" t="s">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="AM5" s="47" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="AN5" s="47" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="AO5" s="46" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="AP5" s="46" t="s">
-        <v>330</v>
+        <v>371</v>
       </c>
       <c r="AQ5" s="47" t="s">
-        <v>331</v>
+        <v>372</v>
       </c>
       <c r="AR5" s="47" t="s">
-        <v>332</v>
+        <v>373</v>
       </c>
       <c r="AS5" s="47" t="s">
-        <v>333</v>
+        <v>374</v>
       </c>
       <c r="AT5" s="47" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="AU5" s="47" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="AV5" s="50" t="s">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="AW5" s="47" t="s">
         <v>50</v>
       </c>
       <c r="AX5" s="50" t="s">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="AY5" s="50" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="AZ5" s="47" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="BA5" s="50" t="s">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="BB5" s="47" t="s">
-        <v>341</v>
+        <v>382</v>
       </c>
       <c r="BC5" s="47" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="BD5" s="50" t="s">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="BE5" s="47" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="BF5" s="50" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="BG5" s="50" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="BH5" s="47" t="s">
-        <v>347</v>
+        <v>388</v>
       </c>
       <c r="BI5" s="50" t="s">
-        <v>348</v>
+        <v>389</v>
       </c>
       <c r="BJ5" s="47" t="s">
-        <v>349</v>
+        <v>390</v>
       </c>
       <c r="BK5" s="47" t="s">
-        <v>350</v>
+        <v>391</v>
       </c>
       <c r="BL5" s="47" t="s">
-        <v>351</v>
+        <v>392</v>
       </c>
       <c r="BM5" s="47" t="s">
+        <v>393</v>
+      </c>
+      <c r="BN5" s="47" t="s">
+        <v>394</v>
+      </c>
+      <c r="BO5" s="47" t="s">
+        <v>395</v>
+      </c>
+      <c r="BP5" s="47" t="s">
+        <v>396</v>
+      </c>
+      <c r="BQ5" s="47" t="s">
+        <v>397</v>
+      </c>
+      <c r="BR5" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="BS5" s="47" t="s">
+        <v>399</v>
+      </c>
+      <c r="BT5" s="47" t="s">
+        <v>400</v>
+      </c>
+      <c r="BU5" s="47" t="s">
+        <v>401</v>
+      </c>
+      <c r="BV5" s="47" t="s">
+        <v>402</v>
+      </c>
+      <c r="BW5" s="47" t="s">
+        <v>403</v>
+      </c>
+      <c r="BX5" s="47" t="s">
+        <v>404</v>
+      </c>
+      <c r="BY5" s="47" t="s">
+        <v>394</v>
+      </c>
+      <c r="BZ5" s="47" t="s">
+        <v>395</v>
+      </c>
+      <c r="CA5" s="47" t="s">
+        <v>396</v>
+      </c>
+      <c r="CB5" s="47" t="s">
+        <v>397</v>
+      </c>
+      <c r="CC5" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="CD5" s="47" t="s">
+        <v>399</v>
+      </c>
+      <c r="CE5" s="47" t="s">
+        <v>400</v>
+      </c>
+      <c r="CF5" s="47" t="s">
+        <v>401</v>
+      </c>
+      <c r="CG5" s="47" t="s">
+        <v>402</v>
+      </c>
+      <c r="CH5" s="47" t="s">
+        <v>405</v>
+      </c>
+      <c r="CI5" s="47" t="s">
+        <v>406</v>
+      </c>
+      <c r="CJ5" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="CK5" s="47" t="s">
+        <v>408</v>
+      </c>
+      <c r="CL5" s="47" t="s">
+        <v>409</v>
+      </c>
+      <c r="CM5" s="47" t="s">
+        <v>410</v>
+      </c>
+      <c r="CN5" s="47" t="s">
+        <v>411</v>
+      </c>
+      <c r="CO5" s="47" t="s">
+        <v>412</v>
+      </c>
+      <c r="CP5" s="47" t="s">
+        <v>413</v>
+      </c>
+      <c r="CQ5" s="47" t="s">
+        <v>414</v>
+      </c>
+      <c r="CR5" s="47" t="s">
+        <v>415</v>
+      </c>
+      <c r="CS5" s="47" t="s">
+        <v>416</v>
+      </c>
+      <c r="CT5" s="47" t="s">
+        <v>417</v>
+      </c>
+      <c r="CU5" s="47" t="s">
+        <v>418</v>
+      </c>
+      <c r="CV5" s="47" t="s">
+        <v>419</v>
+      </c>
+      <c r="CW5" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="CX5" s="47" t="s">
+        <v>421</v>
+      </c>
+      <c r="CY5" s="47" t="s">
+        <v>422</v>
+      </c>
+      <c r="CZ5" s="47" t="s">
+        <v>423</v>
+      </c>
+      <c r="DA5" s="47" t="s">
+        <v>424</v>
+      </c>
+      <c r="DB5" s="47" t="s">
+        <v>425</v>
+      </c>
+      <c r="DC5" s="47" t="s">
+        <v>426</v>
+      </c>
+      <c r="DD5" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="DE5" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="DF5" s="47" t="s">
+        <v>429</v>
+      </c>
+      <c r="DG5" s="47" t="s">
+        <v>430</v>
+      </c>
+      <c r="DH5" s="47" t="s">
+        <v>431</v>
+      </c>
+      <c r="DI5" s="47" t="s">
+        <v>432</v>
+      </c>
+      <c r="DJ5" s="47" t="s">
+        <v>433</v>
+      </c>
+      <c r="DK5" s="47" t="s">
+        <v>434</v>
+      </c>
+      <c r="DL5" s="47" t="s">
+        <v>435</v>
+      </c>
+      <c r="DM5" s="47" t="s">
+        <v>436</v>
+      </c>
+      <c r="DN5" s="47" t="s">
+        <v>437</v>
+      </c>
+      <c r="DO5" s="47" t="s">
+        <v>438</v>
+      </c>
+      <c r="DP5" s="47" t="s">
+        <v>439</v>
+      </c>
+      <c r="DQ5" s="47" t="s">
+        <v>440</v>
+      </c>
+      <c r="DR5" s="47" t="s">
+        <v>441</v>
+      </c>
+      <c r="DS5" s="47" t="s">
+        <v>442</v>
+      </c>
+      <c r="DT5" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="DU5" s="47" t="s">
+        <v>444</v>
+      </c>
+      <c r="DV5" s="47" t="s">
+        <v>445</v>
+      </c>
+      <c r="DW5" s="47" t="s">
+        <v>446</v>
+      </c>
+      <c r="DX5" s="47" t="s">
+        <v>447</v>
+      </c>
+      <c r="DY5" s="47" t="s">
         <v>448</v>
       </c>
-      <c r="BN5" s="47" t="s">
+      <c r="DZ5" s="47" t="s">
+        <v>449</v>
+      </c>
+      <c r="EA5" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="EB5" s="47" t="s">
+        <v>451</v>
+      </c>
+      <c r="EC5" s="47" t="s">
+        <v>452</v>
+      </c>
+      <c r="ED5" s="47" t="s">
+        <v>453</v>
+      </c>
+      <c r="EE5" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="EF5" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="EG5" s="47" t="s">
+        <v>455</v>
+      </c>
+      <c r="EH5" s="47" t="s">
+        <v>456</v>
+      </c>
+      <c r="EI5" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="EJ5" s="47" t="s">
+        <v>457</v>
+      </c>
+      <c r="EK5" s="47" t="s">
+        <v>458</v>
+      </c>
+      <c r="EL5" s="47" t="s">
+        <v>500</v>
+      </c>
+      <c r="EM5" s="47" t="s">
+        <v>459</v>
+      </c>
+      <c r="EN5" s="47" t="s">
+        <v>460</v>
+      </c>
+      <c r="EO5" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="EP5" s="47" t="s">
+        <v>461</v>
+      </c>
+      <c r="EQ5" s="47" t="s">
+        <v>462</v>
+      </c>
+      <c r="ER5" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="ES5" s="47" t="s">
+        <v>463</v>
+      </c>
+      <c r="ET5" s="47" t="s">
+        <v>464</v>
+      </c>
+      <c r="EU5" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="EV5" s="47" t="s">
+        <v>465</v>
+      </c>
+      <c r="EW5" s="47" t="s">
         <v>466</v>
       </c>
-      <c r="BO5" s="47" t="s">
-        <v>451</v>
-      </c>
-      <c r="BP5" s="47" t="s">
-        <v>452</v>
-      </c>
-      <c r="BQ5" s="47" t="s">
+      <c r="EX5" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="EY5" s="47" t="s">
+        <v>368</v>
+      </c>
+      <c r="EZ5" s="47" t="s">
         <v>467</v>
       </c>
-      <c r="BR5" s="47" t="s">
+      <c r="FA5" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="FB5" s="47" t="s">
         <v>468</v>
       </c>
-      <c r="BS5" s="47" t="s">
-        <v>496</v>
-      </c>
-      <c r="BT5" s="47" t="s">
+      <c r="FC5" s="47" t="s">
         <v>469</v>
       </c>
-      <c r="BU5" s="47" t="s">
+      <c r="FD5" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="FE5" s="47" t="s">
+        <v>470</v>
+      </c>
+      <c r="FF5" s="47" t="s">
         <v>471</v>
       </c>
-      <c r="BV5" s="47" t="s">
+      <c r="FG5" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="FH5" s="47" t="s">
+        <v>472</v>
+      </c>
+      <c r="FI5" s="47" t="s">
         <v>473</v>
       </c>
-      <c r="BW5" s="47" t="s">
-        <v>457</v>
-      </c>
-      <c r="BX5" s="47" t="s">
-        <v>352</v>
-      </c>
-      <c r="BY5" s="47" t="s">
-        <v>466</v>
-      </c>
-      <c r="BZ5" s="47" t="s">
-        <v>451</v>
-      </c>
-      <c r="CA5" s="47" t="s">
-        <v>452</v>
-      </c>
-      <c r="CB5" s="47" t="s">
-        <v>467</v>
-      </c>
-      <c r="CC5" s="47" t="s">
-        <v>468</v>
-      </c>
-      <c r="CD5" s="47" t="s">
-        <v>496</v>
-      </c>
-      <c r="CE5" s="47" t="s">
-        <v>469</v>
-      </c>
-      <c r="CF5" s="47" t="s">
-        <v>471</v>
-      </c>
-      <c r="CG5" s="47" t="s">
-        <v>473</v>
-      </c>
-      <c r="CH5" s="47" t="s">
-        <v>353</v>
-      </c>
-      <c r="CI5" s="47" t="s">
-        <v>354</v>
-      </c>
-      <c r="CJ5" s="47" t="s">
-        <v>355</v>
-      </c>
-      <c r="CK5" s="47" t="s">
-        <v>356</v>
-      </c>
-      <c r="CL5" s="47" t="s">
-        <v>357</v>
-      </c>
-      <c r="CM5" s="47" t="s">
-        <v>358</v>
-      </c>
-      <c r="CN5" s="47" t="s">
-        <v>359</v>
-      </c>
-      <c r="CO5" s="47" t="s">
-        <v>360</v>
-      </c>
-      <c r="CP5" s="47" t="s">
-        <v>361</v>
-      </c>
-      <c r="CQ5" s="47" t="s">
-        <v>362</v>
-      </c>
-      <c r="CR5" s="47" t="s">
-        <v>363</v>
-      </c>
-      <c r="CS5" s="47" t="s">
-        <v>364</v>
-      </c>
-      <c r="CT5" s="47" t="s">
-        <v>365</v>
-      </c>
-      <c r="CU5" s="47" t="s">
-        <v>366</v>
-      </c>
-      <c r="CV5" s="47" t="s">
-        <v>367</v>
-      </c>
-      <c r="CW5" s="47" t="s">
-        <v>368</v>
-      </c>
-      <c r="CX5" s="47" t="s">
-        <v>369</v>
-      </c>
-      <c r="CY5" s="47" t="s">
-        <v>370</v>
-      </c>
-      <c r="CZ5" s="47" t="s">
-        <v>371</v>
-      </c>
-      <c r="DA5" s="47" t="s">
-        <v>372</v>
-      </c>
-      <c r="DB5" s="47" t="s">
-        <v>373</v>
-      </c>
-      <c r="DC5" s="47" t="s">
-        <v>374</v>
-      </c>
-      <c r="DD5" s="47" t="s">
-        <v>375</v>
-      </c>
-      <c r="DE5" s="47" t="s">
-        <v>376</v>
-      </c>
-      <c r="DF5" s="47" t="s">
-        <v>377</v>
-      </c>
-      <c r="DG5" s="47" t="s">
-        <v>378</v>
-      </c>
-      <c r="DH5" s="47" t="s">
-        <v>379</v>
-      </c>
-      <c r="DI5" s="47" t="s">
-        <v>380</v>
-      </c>
-      <c r="DJ5" s="47" t="s">
-        <v>381</v>
-      </c>
-      <c r="DK5" s="47" t="s">
-        <v>382</v>
-      </c>
-      <c r="DL5" s="47" t="s">
-        <v>383</v>
-      </c>
-      <c r="DM5" s="47" t="s">
-        <v>384</v>
-      </c>
-      <c r="DN5" s="47" t="s">
-        <v>385</v>
-      </c>
-      <c r="DO5" s="47" t="s">
-        <v>386</v>
-      </c>
-      <c r="DP5" s="47" t="s">
-        <v>387</v>
-      </c>
-      <c r="DQ5" s="47" t="s">
-        <v>388</v>
-      </c>
-      <c r="DR5" s="47" t="s">
-        <v>389</v>
-      </c>
-      <c r="DS5" s="47" t="s">
-        <v>390</v>
-      </c>
-      <c r="DT5" s="47" t="s">
-        <v>391</v>
-      </c>
-      <c r="DU5" s="47" t="s">
-        <v>392</v>
-      </c>
-      <c r="DV5" s="47" t="s">
-        <v>393</v>
-      </c>
-      <c r="DW5" s="47" t="s">
-        <v>394</v>
-      </c>
-      <c r="DX5" s="47" t="s">
-        <v>395</v>
-      </c>
-      <c r="DY5" s="47" t="s">
-        <v>396</v>
-      </c>
-      <c r="DZ5" s="47" t="s">
-        <v>397</v>
-      </c>
-      <c r="EA5" s="47" t="s">
-        <v>398</v>
-      </c>
-      <c r="EB5" s="47" t="s">
-        <v>399</v>
-      </c>
-      <c r="EC5" s="47" t="s">
-        <v>400</v>
-      </c>
-      <c r="ED5" s="47" t="s">
-        <v>401</v>
-      </c>
-      <c r="EE5" s="47" t="s">
-        <v>402</v>
-      </c>
-      <c r="EF5" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="EG5" s="47" t="s">
-        <v>403</v>
-      </c>
-      <c r="EH5" s="47" t="s">
-        <v>404</v>
-      </c>
-      <c r="EI5" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="EJ5" s="47" t="s">
-        <v>405</v>
-      </c>
-      <c r="EK5" s="47" t="s">
-        <v>406</v>
-      </c>
-      <c r="EL5" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="EM5" s="47" t="s">
-        <v>407</v>
-      </c>
-      <c r="EN5" s="47" t="s">
-        <v>408</v>
-      </c>
-      <c r="EO5" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="EP5" s="47" t="s">
-        <v>409</v>
-      </c>
-      <c r="EQ5" s="47" t="s">
-        <v>410</v>
-      </c>
-      <c r="ER5" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="ES5" s="47" t="s">
-        <v>411</v>
-      </c>
-      <c r="ET5" s="47" t="s">
-        <v>412</v>
-      </c>
-      <c r="EU5" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="EV5" s="47" t="s">
-        <v>413</v>
-      </c>
-      <c r="EW5" s="47" t="s">
-        <v>414</v>
-      </c>
-      <c r="EX5" s="47" t="s">
-        <v>96</v>
-      </c>
-      <c r="EY5" s="47" t="s">
-        <v>327</v>
-      </c>
-      <c r="EZ5" s="47" t="s">
-        <v>415</v>
-      </c>
-      <c r="FA5" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="FB5" s="47" t="s">
-        <v>416</v>
-      </c>
-      <c r="FC5" s="47" t="s">
-        <v>417</v>
-      </c>
-      <c r="FD5" s="47" t="s">
-        <v>102</v>
-      </c>
-      <c r="FE5" s="47" t="s">
-        <v>418</v>
-      </c>
-      <c r="FF5" s="47" t="s">
-        <v>419</v>
-      </c>
-      <c r="FG5" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="FH5" s="47" t="s">
-        <v>420</v>
-      </c>
-      <c r="FI5" s="47" t="s">
-        <v>421</v>
-      </c>
       <c r="FJ5" s="47" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="FK5" s="47" t="s">
-        <v>422</v>
+        <v>474</v>
       </c>
       <c r="FL5" s="47" t="s">
-        <v>423</v>
+        <v>475</v>
       </c>
       <c r="FM5" s="47" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="FN5" s="47" t="s">
-        <v>424</v>
+        <v>476</v>
       </c>
       <c r="FO5" s="47" t="s">
-        <v>425</v>
+        <v>477</v>
       </c>
       <c r="FP5" s="47" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="FQ5" s="47" t="s">
-        <v>426</v>
+        <v>478</v>
       </c>
       <c r="FR5" s="47" t="s">
-        <v>427</v>
+        <v>479</v>
       </c>
       <c r="FS5" s="47" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="FT5" s="47" t="s">
-        <v>428</v>
+        <v>480</v>
       </c>
       <c r="FU5" s="47" t="s">
-        <v>429</v>
+        <v>481</v>
       </c>
       <c r="FV5" s="47" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="FW5" s="47" t="s">
-        <v>430</v>
+        <v>482</v>
       </c>
       <c r="FX5" s="47" t="s">
-        <v>431</v>
+        <v>483</v>
       </c>
       <c r="FY5" s="47" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="FZ5" s="47" t="s">
-        <v>432</v>
+        <v>484</v>
       </c>
       <c r="GA5" s="47" t="s">
-        <v>433</v>
+        <v>485</v>
       </c>
       <c r="GB5" s="47" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="GC5" s="47" t="s">
-        <v>434</v>
+        <v>486</v>
       </c>
       <c r="GD5" s="47" t="s">
-        <v>435</v>
+        <v>487</v>
       </c>
       <c r="GE5" s="47" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="GF5" s="43"/>
-      <c r="AMU5" s="2"/>
-      <c r="AMV5" s="2"/>
-      <c r="AMW5" s="2"/>
-      <c r="AMX5" s="2"/>
-      <c r="AMY5" s="2"/>
-      <c r="AMZ5" s="2"/>
-      <c r="ANA5" s="2"/>
-    </row>
-    <row r="6" spans="1:1041" ht="16" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-      <c r="R6"/>
-      <c r="S6"/>
-      <c r="T6"/>
-      <c r="U6"/>
-      <c r="V6"/>
-      <c r="W6"/>
-      <c r="X6"/>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6"/>
-      <c r="AB6"/>
-      <c r="AC6"/>
-      <c r="AD6"/>
-      <c r="AE6"/>
-      <c r="AF6"/>
-      <c r="AG6"/>
-      <c r="AH6"/>
-      <c r="AI6"/>
-      <c r="AJ6"/>
-      <c r="AK6"/>
-      <c r="AL6"/>
-      <c r="AM6"/>
-      <c r="AN6"/>
-      <c r="AO6"/>
-      <c r="AP6"/>
-      <c r="AQ6"/>
-      <c r="AR6"/>
-      <c r="AS6"/>
-      <c r="AT6"/>
-      <c r="AU6"/>
-      <c r="AV6"/>
-      <c r="AW6"/>
-      <c r="AX6"/>
-      <c r="AY6"/>
-      <c r="AZ6"/>
-      <c r="BA6"/>
-      <c r="BB6"/>
-      <c r="BC6"/>
-      <c r="BD6"/>
-      <c r="BE6"/>
-      <c r="BF6"/>
-      <c r="BG6"/>
-      <c r="BH6"/>
-      <c r="BI6"/>
-      <c r="BJ6"/>
-      <c r="BK6"/>
-      <c r="BM6" s="52"/>
-      <c r="BN6"/>
-      <c r="BO6"/>
-      <c r="BP6"/>
-      <c r="BQ6"/>
-      <c r="BR6"/>
-      <c r="BS6"/>
-      <c r="BT6"/>
-      <c r="BU6"/>
-      <c r="BV6"/>
-      <c r="BW6"/>
-      <c r="BX6"/>
-      <c r="BY6"/>
-      <c r="BZ6"/>
-      <c r="CA6"/>
-      <c r="CB6"/>
-      <c r="CC6"/>
-      <c r="CD6"/>
-      <c r="CE6"/>
-      <c r="CF6"/>
-      <c r="CG6"/>
-      <c r="CH6"/>
-      <c r="CI6"/>
-      <c r="CJ6"/>
-      <c r="CK6"/>
-      <c r="CL6"/>
-      <c r="CM6"/>
-      <c r="CN6"/>
-      <c r="CO6"/>
-      <c r="CP6"/>
-      <c r="CQ6"/>
-      <c r="CR6"/>
-      <c r="CS6"/>
-      <c r="CT6"/>
-      <c r="CU6"/>
-      <c r="CV6"/>
-      <c r="CW6"/>
-      <c r="CX6"/>
-      <c r="CY6"/>
-      <c r="CZ6"/>
-      <c r="DA6"/>
-      <c r="DB6"/>
-      <c r="DC6"/>
-      <c r="DD6"/>
-      <c r="DE6"/>
-      <c r="DF6"/>
-      <c r="DG6"/>
-      <c r="DH6"/>
-      <c r="DI6"/>
-      <c r="DJ6"/>
-      <c r="DK6"/>
-      <c r="DL6"/>
-      <c r="DM6"/>
-      <c r="DN6"/>
-      <c r="DO6"/>
-      <c r="DP6"/>
-      <c r="DQ6"/>
-      <c r="DR6"/>
-      <c r="DS6"/>
-      <c r="DT6"/>
-      <c r="DU6"/>
-      <c r="DV6"/>
-      <c r="DW6"/>
-      <c r="DX6"/>
-      <c r="DZ6"/>
-      <c r="EA6"/>
-      <c r="EC6"/>
-      <c r="ED6"/>
-      <c r="EE6"/>
-      <c r="EF6"/>
-      <c r="EG6"/>
-      <c r="EI6"/>
-      <c r="EJ6"/>
-      <c r="EL6"/>
-      <c r="EM6"/>
-      <c r="EO6"/>
-      <c r="EP6"/>
-      <c r="ES6"/>
-      <c r="EU6"/>
-      <c r="EV6"/>
-      <c r="EX6"/>
-      <c r="EY6"/>
-      <c r="FA6"/>
-      <c r="FB6"/>
-      <c r="FD6"/>
-      <c r="FE6"/>
-      <c r="FG6"/>
-      <c r="FH6"/>
-      <c r="FJ6"/>
-      <c r="FK6"/>
-      <c r="FM6"/>
-      <c r="FN6"/>
-      <c r="FP6"/>
-      <c r="FQ6"/>
-      <c r="FS6"/>
-      <c r="FT6"/>
-      <c r="FV6"/>
-      <c r="FW6"/>
-      <c r="FY6"/>
-      <c r="FZ6"/>
-      <c r="GA6"/>
-      <c r="GB6"/>
-      <c r="GC6"/>
-      <c r="GD6"/>
-      <c r="GE6"/>
-      <c r="GF6"/>
-      <c r="GG6"/>
-      <c r="GH6"/>
-      <c r="GI6"/>
-      <c r="GJ6"/>
-      <c r="GK6"/>
-      <c r="GL6"/>
-      <c r="GM6"/>
-      <c r="GN6"/>
-      <c r="GO6"/>
-      <c r="GP6"/>
-      <c r="GQ6"/>
-      <c r="GR6"/>
-      <c r="GS6"/>
-      <c r="GT6"/>
-      <c r="GU6"/>
-      <c r="GV6"/>
-      <c r="GW6"/>
-      <c r="GX6"/>
-      <c r="GY6"/>
-      <c r="GZ6"/>
-      <c r="HA6"/>
-      <c r="HB6"/>
-      <c r="HC6"/>
-      <c r="HD6"/>
-      <c r="HE6"/>
-      <c r="HF6"/>
-      <c r="HG6"/>
-      <c r="HH6"/>
-      <c r="HI6"/>
-      <c r="HJ6"/>
-      <c r="HK6"/>
-      <c r="HL6"/>
-      <c r="HM6"/>
-      <c r="HN6"/>
-      <c r="HO6"/>
-      <c r="HP6"/>
-      <c r="HQ6"/>
-      <c r="HR6"/>
-      <c r="HS6"/>
-      <c r="HT6"/>
-      <c r="HU6"/>
-      <c r="HV6"/>
-      <c r="HW6"/>
-      <c r="HX6"/>
-      <c r="HY6"/>
-      <c r="HZ6"/>
-      <c r="IA6"/>
-      <c r="IB6"/>
-      <c r="IC6"/>
-      <c r="ID6"/>
-      <c r="IE6"/>
-      <c r="IF6"/>
-      <c r="IG6"/>
-      <c r="IH6"/>
-      <c r="II6"/>
-      <c r="IJ6"/>
-      <c r="IK6"/>
-      <c r="IL6"/>
-      <c r="IM6"/>
-      <c r="IN6"/>
-      <c r="IO6"/>
-      <c r="IP6"/>
-      <c r="IQ6"/>
-      <c r="IR6"/>
-      <c r="IS6"/>
-      <c r="IT6"/>
-      <c r="IU6"/>
-      <c r="IV6"/>
-      <c r="IW6"/>
-      <c r="IX6"/>
-      <c r="IY6"/>
-      <c r="IZ6"/>
-      <c r="JA6"/>
-      <c r="JB6"/>
-      <c r="JC6"/>
-      <c r="JD6"/>
-      <c r="JE6"/>
-      <c r="JF6"/>
-      <c r="JG6"/>
-      <c r="JH6"/>
-      <c r="JI6"/>
-      <c r="JJ6"/>
-      <c r="JK6"/>
-      <c r="JL6"/>
-      <c r="JM6"/>
-      <c r="JN6"/>
-      <c r="JO6"/>
-      <c r="JP6"/>
-      <c r="JQ6"/>
-      <c r="JR6"/>
-      <c r="JS6"/>
-      <c r="JT6"/>
-      <c r="JU6"/>
-      <c r="JV6"/>
-      <c r="JW6"/>
-      <c r="JX6"/>
-      <c r="JY6"/>
-      <c r="JZ6"/>
-      <c r="KA6"/>
-      <c r="KB6"/>
-      <c r="KC6"/>
-      <c r="KD6"/>
-      <c r="KE6"/>
-      <c r="KF6"/>
-      <c r="KG6"/>
-      <c r="KH6"/>
-      <c r="KI6"/>
-      <c r="KJ6"/>
-      <c r="KK6"/>
-      <c r="KL6"/>
-      <c r="KM6"/>
-      <c r="KN6"/>
-      <c r="KO6"/>
-      <c r="KP6"/>
-      <c r="KQ6"/>
-      <c r="KR6"/>
-      <c r="KS6"/>
-      <c r="KT6"/>
-      <c r="KU6"/>
-      <c r="KV6"/>
-      <c r="KW6"/>
-      <c r="KX6"/>
-      <c r="KY6"/>
-      <c r="KZ6"/>
-      <c r="LA6"/>
-      <c r="LB6"/>
-      <c r="LC6"/>
-      <c r="LD6"/>
-      <c r="LE6"/>
-      <c r="LF6"/>
-      <c r="LG6"/>
-      <c r="LH6"/>
-      <c r="LI6"/>
-      <c r="LJ6"/>
-      <c r="LK6"/>
-      <c r="LL6"/>
-      <c r="LM6"/>
-      <c r="LN6"/>
-      <c r="LO6"/>
-      <c r="LP6"/>
-      <c r="LQ6"/>
-      <c r="LR6"/>
-      <c r="LS6"/>
-      <c r="LT6"/>
-      <c r="LU6"/>
-      <c r="LV6"/>
-      <c r="LW6"/>
-      <c r="LX6"/>
-      <c r="LY6"/>
-      <c r="LZ6"/>
-      <c r="MA6"/>
-      <c r="MB6"/>
-      <c r="MC6"/>
-      <c r="MD6"/>
-      <c r="ME6"/>
-      <c r="MF6"/>
-      <c r="MG6"/>
-      <c r="MH6"/>
-      <c r="MI6"/>
-      <c r="MJ6"/>
-      <c r="MK6"/>
-      <c r="ML6"/>
-      <c r="MM6"/>
-      <c r="MN6"/>
-      <c r="MO6"/>
-      <c r="MP6"/>
-      <c r="MQ6"/>
-      <c r="MR6"/>
-      <c r="MS6"/>
-      <c r="MT6"/>
-      <c r="MU6"/>
-      <c r="MV6"/>
-      <c r="MW6"/>
-      <c r="MX6"/>
-      <c r="MY6"/>
-      <c r="MZ6"/>
-      <c r="NA6"/>
-      <c r="NB6"/>
-      <c r="NC6"/>
-      <c r="ND6"/>
-      <c r="NE6"/>
-      <c r="NF6"/>
-      <c r="NG6"/>
-      <c r="NH6"/>
-      <c r="NI6"/>
-      <c r="NJ6"/>
-      <c r="NK6"/>
-      <c r="NL6"/>
-      <c r="NM6"/>
-      <c r="NN6"/>
-      <c r="NO6"/>
-      <c r="NP6"/>
-      <c r="NQ6"/>
-      <c r="NR6"/>
-      <c r="NS6"/>
-      <c r="NT6"/>
-      <c r="NU6"/>
-      <c r="NV6"/>
-      <c r="NW6"/>
-      <c r="NX6"/>
-      <c r="NY6"/>
-      <c r="NZ6"/>
-      <c r="OA6"/>
-      <c r="OB6"/>
-      <c r="OC6"/>
-      <c r="OD6"/>
-      <c r="OE6"/>
-      <c r="OF6"/>
-      <c r="OG6"/>
-      <c r="OH6"/>
-      <c r="OI6"/>
-      <c r="OJ6"/>
-      <c r="OK6"/>
-      <c r="OL6"/>
-      <c r="OM6"/>
-      <c r="ON6"/>
-      <c r="OO6"/>
-      <c r="OP6"/>
-      <c r="OQ6"/>
-      <c r="OR6"/>
-      <c r="OS6"/>
-      <c r="OT6"/>
-      <c r="OU6"/>
-      <c r="OV6"/>
-      <c r="OW6"/>
-      <c r="OX6"/>
-      <c r="OY6"/>
-      <c r="OZ6"/>
-      <c r="PA6"/>
-      <c r="PB6"/>
-      <c r="PC6"/>
-      <c r="PD6"/>
-      <c r="PE6"/>
-      <c r="PF6"/>
-      <c r="PG6"/>
-      <c r="PH6"/>
-      <c r="PI6"/>
-      <c r="PJ6"/>
-      <c r="PK6"/>
-      <c r="PL6"/>
-      <c r="PM6"/>
-      <c r="PN6"/>
-      <c r="PO6"/>
-      <c r="PP6"/>
-      <c r="PQ6"/>
-      <c r="PR6"/>
-      <c r="PS6"/>
-      <c r="PT6"/>
-      <c r="PU6"/>
-      <c r="PV6"/>
-      <c r="PW6"/>
-      <c r="PX6"/>
-      <c r="PY6"/>
-      <c r="PZ6"/>
-      <c r="QA6"/>
-      <c r="QB6"/>
-      <c r="QC6"/>
-      <c r="QD6"/>
-      <c r="QE6"/>
-      <c r="QF6"/>
-      <c r="QG6"/>
-      <c r="QH6"/>
-      <c r="QI6"/>
-      <c r="QJ6"/>
-      <c r="QK6"/>
-      <c r="QL6"/>
-      <c r="QM6"/>
-      <c r="QN6"/>
-      <c r="QO6"/>
-      <c r="QP6"/>
-      <c r="QQ6"/>
-      <c r="QR6"/>
-      <c r="QS6"/>
-      <c r="QT6"/>
-      <c r="QU6"/>
-      <c r="QV6"/>
-      <c r="QW6"/>
-      <c r="QX6"/>
-      <c r="QY6"/>
-      <c r="QZ6"/>
-      <c r="RA6"/>
-      <c r="RB6"/>
-      <c r="RC6"/>
-      <c r="RD6"/>
-      <c r="RE6"/>
-      <c r="RF6"/>
-      <c r="RG6"/>
-      <c r="RH6"/>
-      <c r="RI6"/>
-      <c r="RJ6"/>
-      <c r="RK6"/>
-      <c r="RL6"/>
-      <c r="RM6"/>
-      <c r="RN6"/>
-      <c r="RO6"/>
-      <c r="RP6"/>
-      <c r="RQ6"/>
-      <c r="RR6"/>
-      <c r="RS6"/>
-      <c r="RT6"/>
-      <c r="RU6"/>
-      <c r="RV6"/>
-      <c r="RW6"/>
-      <c r="RX6"/>
-      <c r="RY6"/>
-      <c r="RZ6"/>
-      <c r="SA6"/>
-      <c r="SB6"/>
-      <c r="SC6"/>
-      <c r="SD6"/>
-      <c r="SE6"/>
-      <c r="SF6"/>
-      <c r="SG6"/>
-      <c r="SH6"/>
-      <c r="SI6"/>
-      <c r="SJ6"/>
-      <c r="SK6"/>
-      <c r="SL6"/>
-      <c r="SM6"/>
-      <c r="SN6"/>
-      <c r="SO6"/>
-      <c r="SP6"/>
-      <c r="SQ6"/>
-      <c r="SR6"/>
-      <c r="SS6"/>
-      <c r="ST6"/>
-      <c r="SU6"/>
-      <c r="SV6"/>
-      <c r="SW6"/>
-      <c r="SX6"/>
-      <c r="SY6"/>
-      <c r="SZ6"/>
-      <c r="TA6"/>
-      <c r="TB6"/>
-      <c r="TC6"/>
-      <c r="TD6"/>
-      <c r="TE6"/>
-      <c r="TF6"/>
-      <c r="TG6"/>
-      <c r="TH6"/>
-      <c r="TI6"/>
-      <c r="TJ6"/>
-      <c r="TK6"/>
-      <c r="TL6"/>
-      <c r="TM6"/>
-      <c r="TN6"/>
-      <c r="TO6"/>
-      <c r="TP6"/>
-      <c r="TQ6"/>
-      <c r="TR6"/>
-      <c r="TS6"/>
-      <c r="TT6"/>
-      <c r="TU6"/>
-      <c r="TV6"/>
-      <c r="TW6"/>
-      <c r="TX6"/>
-      <c r="TY6"/>
-      <c r="TZ6"/>
-      <c r="UA6"/>
-      <c r="UB6"/>
-      <c r="UC6"/>
-      <c r="UD6"/>
-      <c r="UE6"/>
-      <c r="UF6"/>
-      <c r="UG6"/>
-      <c r="UH6"/>
-      <c r="UI6"/>
-      <c r="UJ6"/>
-      <c r="UK6"/>
-      <c r="UL6"/>
-      <c r="UM6"/>
-      <c r="UN6"/>
-      <c r="UO6"/>
-      <c r="UP6"/>
-      <c r="UQ6"/>
-      <c r="UR6"/>
-      <c r="US6"/>
-      <c r="UT6"/>
-      <c r="UU6"/>
-      <c r="UV6"/>
-      <c r="UW6"/>
-      <c r="UX6"/>
-      <c r="UY6"/>
-      <c r="UZ6"/>
-      <c r="VA6"/>
-      <c r="VB6"/>
-      <c r="VC6"/>
-      <c r="VD6"/>
-      <c r="VE6"/>
-      <c r="VF6"/>
-      <c r="VG6"/>
-      <c r="VH6"/>
-      <c r="VI6"/>
-      <c r="VJ6"/>
-      <c r="VK6"/>
-      <c r="VL6"/>
-      <c r="VM6"/>
-      <c r="VN6"/>
-      <c r="VO6"/>
-      <c r="VP6"/>
-      <c r="VQ6"/>
-      <c r="VR6"/>
-      <c r="VS6"/>
-      <c r="VT6"/>
-      <c r="VU6"/>
-      <c r="VV6"/>
-      <c r="VW6"/>
-      <c r="VX6"/>
-      <c r="VY6"/>
-      <c r="VZ6"/>
-      <c r="WA6"/>
-      <c r="WB6"/>
-      <c r="WC6"/>
-      <c r="WD6"/>
-      <c r="WE6"/>
-      <c r="WF6"/>
-      <c r="WG6"/>
-      <c r="WH6"/>
-      <c r="WI6"/>
-      <c r="WJ6"/>
-      <c r="WK6"/>
-      <c r="WL6"/>
-      <c r="WM6"/>
-      <c r="WN6"/>
-      <c r="WO6"/>
-      <c r="WP6"/>
-      <c r="WQ6"/>
-      <c r="WR6"/>
-      <c r="WS6"/>
-      <c r="WT6"/>
-      <c r="WU6"/>
-      <c r="WV6"/>
-      <c r="WW6"/>
-      <c r="WX6"/>
-      <c r="WY6"/>
-      <c r="WZ6"/>
-      <c r="XA6"/>
-      <c r="XB6"/>
-      <c r="XC6"/>
-      <c r="XD6"/>
-      <c r="XE6"/>
-      <c r="XF6"/>
-      <c r="XG6"/>
-      <c r="XH6"/>
-      <c r="XI6"/>
-      <c r="XJ6"/>
-      <c r="XK6"/>
-      <c r="XL6"/>
-      <c r="XM6"/>
-      <c r="XN6"/>
-      <c r="XO6"/>
-      <c r="XP6"/>
-      <c r="XQ6"/>
-      <c r="XR6"/>
-      <c r="XS6"/>
-      <c r="XT6"/>
-      <c r="XU6"/>
-      <c r="XV6"/>
-      <c r="XW6"/>
-      <c r="XX6"/>
-      <c r="XY6"/>
-      <c r="XZ6"/>
-      <c r="YA6"/>
-      <c r="YB6"/>
-      <c r="YC6"/>
-      <c r="YD6"/>
-      <c r="YE6"/>
-      <c r="YF6"/>
-      <c r="YG6"/>
-      <c r="YH6"/>
-      <c r="YI6"/>
-      <c r="YJ6"/>
-      <c r="YK6"/>
-      <c r="YL6"/>
-      <c r="YM6"/>
-      <c r="YN6"/>
-      <c r="YO6"/>
-      <c r="YP6"/>
-      <c r="YQ6"/>
-      <c r="YR6"/>
-      <c r="YS6"/>
-      <c r="YT6"/>
-      <c r="YU6"/>
-      <c r="YV6"/>
-      <c r="YW6"/>
-      <c r="YX6"/>
-      <c r="YY6"/>
-      <c r="YZ6"/>
-      <c r="ZA6"/>
-      <c r="ZB6"/>
-      <c r="ZC6"/>
-      <c r="ZD6"/>
-      <c r="ZE6"/>
-      <c r="ZF6"/>
-      <c r="ZG6"/>
-      <c r="ZH6"/>
-      <c r="ZI6"/>
-      <c r="ZJ6"/>
-      <c r="ZK6"/>
-      <c r="ZL6"/>
-      <c r="ZM6"/>
-      <c r="ZN6"/>
-      <c r="ZO6"/>
-      <c r="ZP6"/>
-      <c r="ZQ6"/>
-      <c r="ZR6"/>
-      <c r="ZS6"/>
-      <c r="ZT6"/>
-      <c r="ZU6"/>
-      <c r="ZV6"/>
-      <c r="ZW6"/>
-      <c r="ZX6"/>
-      <c r="ZY6"/>
-      <c r="ZZ6"/>
-      <c r="AAA6"/>
-      <c r="AAB6"/>
-      <c r="AAC6"/>
-      <c r="AAD6"/>
-      <c r="AAE6"/>
-      <c r="AAF6"/>
-      <c r="AAG6"/>
-      <c r="AAH6"/>
-      <c r="AAI6"/>
-      <c r="AAJ6"/>
-      <c r="AAK6"/>
-      <c r="AAL6"/>
-      <c r="AAM6"/>
-      <c r="AAN6"/>
-      <c r="AAO6"/>
-      <c r="AAP6"/>
-      <c r="AAQ6"/>
-      <c r="AAR6"/>
-      <c r="AAS6"/>
-      <c r="AAT6"/>
-      <c r="AAU6"/>
-      <c r="AAV6"/>
-      <c r="AAW6"/>
-      <c r="AAX6"/>
-      <c r="AAY6"/>
-      <c r="AAZ6"/>
-      <c r="ABA6"/>
-      <c r="ABB6"/>
-      <c r="ABC6"/>
-      <c r="ABD6"/>
-      <c r="ABE6"/>
-      <c r="ABF6"/>
-      <c r="ABG6"/>
-      <c r="ABH6"/>
-      <c r="ABI6"/>
-      <c r="ABJ6"/>
-      <c r="ABK6"/>
-      <c r="ABL6"/>
-      <c r="ABM6"/>
-      <c r="ABN6"/>
-      <c r="ABO6"/>
-      <c r="ABP6"/>
-      <c r="ABQ6"/>
-      <c r="ABR6"/>
-      <c r="ABS6"/>
-      <c r="ABT6"/>
-      <c r="ABU6"/>
-      <c r="ABV6"/>
-      <c r="ABW6"/>
-      <c r="ABX6"/>
-      <c r="ABY6"/>
-      <c r="ABZ6"/>
-      <c r="ACA6"/>
-      <c r="ACB6"/>
-      <c r="ACC6"/>
-      <c r="ACD6"/>
-      <c r="ACE6"/>
-      <c r="ACF6"/>
-      <c r="ACG6"/>
-      <c r="ACH6"/>
-      <c r="ACI6"/>
-      <c r="ACJ6"/>
-      <c r="ACK6"/>
-      <c r="ACL6"/>
-      <c r="ACM6"/>
-      <c r="ACN6"/>
-      <c r="ACO6"/>
-      <c r="ACP6"/>
-      <c r="ACQ6"/>
-      <c r="ACR6"/>
-      <c r="ACS6"/>
-      <c r="ACT6"/>
-      <c r="ACU6"/>
-      <c r="ACV6"/>
-      <c r="ACW6"/>
-      <c r="ACX6"/>
-      <c r="ACY6"/>
-      <c r="ACZ6"/>
-      <c r="ADA6"/>
-      <c r="ADB6"/>
-      <c r="ADC6"/>
-      <c r="ADD6"/>
-      <c r="ADE6"/>
-      <c r="ADF6"/>
-      <c r="ADG6"/>
-      <c r="ADH6"/>
-      <c r="ADI6"/>
-      <c r="ADJ6"/>
-      <c r="ADK6"/>
-      <c r="ADL6"/>
-      <c r="ADM6"/>
-      <c r="ADN6"/>
-      <c r="ADO6"/>
-      <c r="ADP6"/>
-      <c r="ADQ6"/>
-      <c r="ADR6"/>
-      <c r="ADS6"/>
-      <c r="ADT6"/>
-      <c r="ADU6"/>
-      <c r="ADV6"/>
-      <c r="ADW6"/>
-      <c r="ADX6"/>
-      <c r="ADY6"/>
-      <c r="ADZ6"/>
-      <c r="AEA6"/>
-      <c r="AEB6"/>
-      <c r="AEC6"/>
-      <c r="AED6"/>
-      <c r="AEE6"/>
-      <c r="AEF6"/>
-      <c r="AEG6"/>
-      <c r="AEH6"/>
-      <c r="AEI6"/>
-      <c r="AEJ6"/>
-      <c r="AEK6"/>
-      <c r="AEL6"/>
-      <c r="AEM6"/>
-      <c r="AEN6"/>
-      <c r="AEO6"/>
-      <c r="AEP6"/>
-      <c r="AEQ6"/>
-      <c r="AER6"/>
-      <c r="AES6"/>
-      <c r="AET6"/>
-      <c r="AEU6"/>
-      <c r="AEV6"/>
-      <c r="AEW6"/>
-      <c r="AEX6"/>
-      <c r="AEY6"/>
-      <c r="AEZ6"/>
-      <c r="AFA6"/>
-      <c r="AFB6"/>
-      <c r="AFC6"/>
-      <c r="AFD6"/>
-      <c r="AFE6"/>
-      <c r="AFF6"/>
-      <c r="AFG6"/>
-      <c r="AFH6"/>
-      <c r="AFI6"/>
-      <c r="AFJ6"/>
-      <c r="AFK6"/>
-      <c r="AFL6"/>
-      <c r="AFM6"/>
-      <c r="AFN6"/>
-      <c r="AFO6"/>
-      <c r="AFP6"/>
-      <c r="AFQ6"/>
-      <c r="AFR6"/>
-      <c r="AFS6"/>
-      <c r="AFT6"/>
-      <c r="AFU6"/>
-      <c r="AFV6"/>
-      <c r="AFW6"/>
-      <c r="AFX6"/>
-      <c r="AFY6"/>
-      <c r="AFZ6"/>
-      <c r="AGA6"/>
-      <c r="AGB6"/>
-      <c r="AGC6"/>
-      <c r="AGD6"/>
-      <c r="AGE6"/>
-      <c r="AGF6"/>
-      <c r="AGG6"/>
-      <c r="AGH6"/>
-      <c r="AGI6"/>
-      <c r="AGJ6"/>
-      <c r="AGK6"/>
-      <c r="AGL6"/>
-      <c r="AGM6"/>
-      <c r="AGN6"/>
-      <c r="AGO6"/>
-      <c r="AGP6"/>
-      <c r="AGQ6"/>
-      <c r="AGR6"/>
-      <c r="AGS6"/>
-      <c r="AGT6"/>
-      <c r="AGU6"/>
-      <c r="AGV6"/>
-      <c r="AGW6"/>
-      <c r="AGX6"/>
-      <c r="AGY6"/>
-      <c r="AGZ6"/>
-      <c r="AHA6"/>
-      <c r="AHB6"/>
-      <c r="AHC6"/>
-      <c r="AHD6"/>
-      <c r="AHE6"/>
-      <c r="AHF6"/>
-      <c r="AHG6"/>
-      <c r="AHH6"/>
-      <c r="AHI6"/>
-      <c r="AHJ6"/>
-      <c r="AHK6"/>
-      <c r="AHL6"/>
-      <c r="AHM6"/>
-      <c r="AHN6"/>
-      <c r="AHO6"/>
-      <c r="AHP6"/>
-      <c r="AHQ6"/>
-      <c r="AHR6"/>
-      <c r="AHS6"/>
-      <c r="AHT6"/>
-      <c r="AHU6"/>
-      <c r="AHV6"/>
-      <c r="AHW6"/>
-      <c r="AHX6"/>
-      <c r="AHY6"/>
-      <c r="AHZ6"/>
-      <c r="AIA6"/>
-      <c r="AIB6"/>
-      <c r="AIC6"/>
-      <c r="AID6"/>
-      <c r="AIE6"/>
-      <c r="AIF6"/>
-      <c r="AIG6"/>
-      <c r="AIH6"/>
-      <c r="AII6"/>
-      <c r="AIJ6"/>
-      <c r="AIK6"/>
-      <c r="AIL6"/>
-      <c r="AIM6"/>
-      <c r="AIN6"/>
-      <c r="AIO6"/>
-      <c r="AIP6"/>
-      <c r="AIQ6"/>
-      <c r="AIR6"/>
-      <c r="AIS6"/>
-      <c r="AIT6"/>
-      <c r="AIU6"/>
-      <c r="AIV6"/>
-      <c r="AIW6"/>
-      <c r="AIX6"/>
-      <c r="AIY6"/>
-      <c r="AIZ6"/>
-      <c r="AJA6"/>
-      <c r="AJB6"/>
-      <c r="AJC6"/>
-      <c r="AJD6"/>
-      <c r="AJE6"/>
-      <c r="AJF6"/>
-      <c r="AJG6"/>
-      <c r="AJH6"/>
-      <c r="AJI6"/>
-      <c r="AJJ6"/>
-      <c r="AJK6"/>
-      <c r="AJL6"/>
-      <c r="AJM6"/>
-      <c r="AJN6"/>
-      <c r="AJO6"/>
-      <c r="AJP6"/>
-      <c r="AJQ6"/>
-      <c r="AJR6"/>
-      <c r="AJS6"/>
-      <c r="AJT6"/>
-      <c r="AJU6"/>
-      <c r="AJV6"/>
-      <c r="AJW6"/>
-      <c r="AJX6"/>
-      <c r="AJY6"/>
-      <c r="AJZ6"/>
-      <c r="AKA6"/>
-      <c r="AKB6"/>
-      <c r="AKC6"/>
-      <c r="AKD6"/>
-      <c r="AKE6"/>
-      <c r="AKF6"/>
-      <c r="AKG6"/>
-      <c r="AKH6"/>
-      <c r="AKI6"/>
-      <c r="AKJ6"/>
-      <c r="AKK6"/>
-      <c r="AKL6"/>
-      <c r="AKM6"/>
-      <c r="AKN6"/>
-      <c r="AKO6"/>
-      <c r="AKP6"/>
-      <c r="AKQ6"/>
-      <c r="AKR6"/>
-      <c r="AKS6"/>
-      <c r="AKT6"/>
-      <c r="AKU6"/>
-      <c r="AKV6"/>
-      <c r="AKW6"/>
-      <c r="AKX6"/>
-      <c r="AKY6"/>
-      <c r="AKZ6"/>
-      <c r="ALA6"/>
-      <c r="ALB6"/>
-      <c r="ALC6"/>
-      <c r="ALD6"/>
-      <c r="ALE6"/>
-      <c r="ALF6"/>
-      <c r="ALG6"/>
-      <c r="ALH6"/>
-      <c r="ALI6"/>
-      <c r="ALJ6"/>
-      <c r="ALK6"/>
-      <c r="ALL6"/>
-      <c r="ALM6"/>
-      <c r="ALN6"/>
-      <c r="ALO6"/>
-      <c r="ALP6"/>
-      <c r="ALQ6"/>
-      <c r="ALR6"/>
-      <c r="ALS6"/>
-      <c r="ALT6"/>
-      <c r="ALU6"/>
-      <c r="ALV6"/>
-      <c r="ALW6"/>
-      <c r="ALX6"/>
-      <c r="ALY6"/>
-      <c r="ALZ6"/>
-      <c r="AMA6"/>
-      <c r="AMB6"/>
-      <c r="AMC6"/>
-      <c r="AMD6"/>
-      <c r="AME6"/>
-      <c r="AMF6"/>
-      <c r="AMG6"/>
-      <c r="AMH6"/>
-      <c r="AMI6"/>
-      <c r="AMJ6"/>
-      <c r="AMK6"/>
-      <c r="AML6"/>
-      <c r="AMM6"/>
-      <c r="AMN6"/>
-      <c r="AMO6"/>
-      <c r="AMP6"/>
-      <c r="AMQ6"/>
-      <c r="AMR6"/>
-      <c r="AMS6"/>
-      <c r="AMT6"/>
-    </row>
-    <row r="7" spans="1:1041" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:188" x14ac:dyDescent="0.2">
+      <c r="BM6" s="51"/>
+      <c r="BN6" s="2"/>
+    </row>
+    <row r="7" spans="1:188" x14ac:dyDescent="0.2">
       <c r="DY7" s="2"/>
       <c r="EB7" s="2"/>
       <c r="EH7" s="2"/>
@@ -5803,7 +4796,7 @@
       <c r="FU7" s="2"/>
       <c r="FX7" s="2"/>
     </row>
-    <row r="8" spans="1:1041" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:188" x14ac:dyDescent="0.2">
       <c r="DY8" s="2"/>
       <c r="EB8" s="2"/>
       <c r="EH8" s="2"/>
@@ -5823,7 +4816,7 @@
       <c r="FU8" s="2"/>
       <c r="FX8" s="2"/>
     </row>
-    <row r="9" spans="1:1041" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:188" x14ac:dyDescent="0.2">
       <c r="DY9" s="2"/>
       <c r="EB9" s="2"/>
       <c r="EH9" s="2"/>
@@ -5843,7 +4836,7 @@
       <c r="FU9" s="2"/>
       <c r="FX9" s="2"/>
     </row>
-    <row r="10" spans="1:1041" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:188" x14ac:dyDescent="0.2">
       <c r="DY10" s="2"/>
       <c r="EB10" s="2"/>
       <c r="EH10" s="2"/>
@@ -5863,7 +4856,7 @@
       <c r="FU10" s="2"/>
       <c r="FX10" s="2"/>
     </row>
-    <row r="11" spans="1:1041" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:188" x14ac:dyDescent="0.2">
       <c r="DY11" s="2"/>
       <c r="EB11" s="2"/>
       <c r="EH11" s="2"/>
@@ -5883,7 +4876,7 @@
       <c r="FU11" s="2"/>
       <c r="FX11" s="2"/>
     </row>
-    <row r="12" spans="1:1041" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:188" x14ac:dyDescent="0.2">
       <c r="DY12" s="2"/>
       <c r="EB12" s="2"/>
       <c r="EH12" s="2"/>
@@ -5903,7 +4896,7 @@
       <c r="FU12" s="2"/>
       <c r="FX12" s="2"/>
     </row>
-    <row r="13" spans="1:1041" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:188" x14ac:dyDescent="0.2">
       <c r="DY13" s="2"/>
       <c r="EB13" s="2"/>
       <c r="EH13" s="2"/>
@@ -5923,7 +4916,7 @@
       <c r="FU13" s="2"/>
       <c r="FX13" s="2"/>
     </row>
-    <row r="14" spans="1:1041" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:188" x14ac:dyDescent="0.2">
       <c r="DY14" s="2"/>
       <c r="EB14" s="2"/>
       <c r="EH14" s="2"/>
@@ -5943,7 +4936,7 @@
       <c r="FU14" s="2"/>
       <c r="FX14" s="2"/>
     </row>
-    <row r="15" spans="1:1041" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:188" x14ac:dyDescent="0.2">
       <c r="DY15" s="2"/>
       <c r="EB15" s="2"/>
       <c r="EH15" s="2"/>
@@ -5963,7 +4956,7 @@
       <c r="FU15" s="2"/>
       <c r="FX15" s="2"/>
     </row>
-    <row r="16" spans="1:1041" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:188" x14ac:dyDescent="0.2">
       <c r="DY16" s="2"/>
       <c r="EB16" s="2"/>
       <c r="EH16" s="2"/>
@@ -25769,7 +24762,7 @@
       <formula1>"Class,Collection,File,Fonds,Item,Other Level,Record Group,Series,Sub-Fonds,Sub-Group,Sub-Series"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L1005 BX6:BX1005 BN7:BN1005 BL7:BL1000" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX6:BX1005 L6:L1005 BL6:BL1000" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"FALSE,TRUE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -25785,39 +24778,29 @@
       <formula1>"FALSE,TRUE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BZ6:BZ1005 BO6:BO1005" xr:uid="{5D76880C-C02E-A042-8CB3-F8ED38E8A491}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO6:BO1005 BZ6:BZ1005" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"none,onLoad,onRequest,other"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CA6:CA1005 BP6:BP1005" xr:uid="{AE634187-8996-A241-9F77-3E1846E30705}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BP6:BP1005 CA6:CA1005" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"embed,new,none,other,replace"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CJ6:CJ1005 CN6:CN1005 CR6:CR1005 CV6:CV1005 CZ6:CZ1005 DD6:DD1005 DH6:DH1005 DL6:DL1005 DP6:DP1005 DT6:DT1005" xr:uid="{C320EC5E-F1BE-724F-8666-9989C0D62631}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CJ6:CJ1005 CN6:CN1005 CR6:CR1005 CV6:CV1005 CZ6:CZ1005 DD6:DD1005 DH6:DH1005 DL6:DL1005 DP6:DP1005 DT6:DT1005" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"Creator,Source,Subject"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU6:BU1005 CF6" xr:uid="{46597498-D06D-A846-86D0-FFB419792FF2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU6:BU7 CF6 BU8:BU1005" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>"MD5,SHA-1,SHA-256,SHA-384,SHA-512"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL6" xr:uid="{F9604B1C-3897-B94F-A8D9-2113A4292C59}">
-      <formula1>"FALSE,TRUE"</formula1>
+    <dataValidation operator="equal" allowBlank="1" showErrorMessage="1" sqref="BN1:BN1005 CG1:CG1005 CC1:CC1005" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
-          <x14:formula1>
-            <xm:f>Sheet2!$A$2:$A$4</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>CG7:CG1005 CC7:CC1005</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -25830,48 +24813,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
-        <v>436</v>
+      <c r="A1" s="52" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>437</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>438</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>439</v>
+        <v>491</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>440</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>441</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>442</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>443</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -25885,22 +24868,22 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>444</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>445</v>
+        <v>497</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>446</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/frontend/public/bulk_import_templates/bulk_import_template.xlsx
+++ b/frontend/public/bulk_import_templates/bulk_import_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zeffmorgan/src/lyrasis/archivesspace/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D71783-F4B3-4846-9F94-907FE5F5F64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B037063-3885-AD41-A1FB-86137D1EC3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34560" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="505">
   <si>
     <t>This is the template for importing archival objects using the bulk_import ("Load SpreadSheet").  You may replace this line with something of your choosing after you've copied the file for your use.</t>
   </si>
@@ -1540,6 +1540,18 @@
   </si>
   <si>
     <t>Access Restrictions Type(1)</t>
+  </si>
+  <si>
+    <t>b_userestrict</t>
+  </si>
+  <si>
+    <t>e_userestrict</t>
+  </si>
+  <si>
+    <t>Use Restrictions Begin Date</t>
+  </si>
+  <si>
+    <t>Use Restrictions End Date</t>
   </si>
 </sst>
 </file>
@@ -2353,7 +2365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ1005"/>
+  <dimension ref="A1:AML1005"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" style="1" customWidth="1"/>
@@ -2495,10 +2507,10 @@
     <col min="178" max="178" width="10.1640625" style="2" customWidth="1"/>
     <col min="179" max="179" width="17.6640625" style="2" customWidth="1"/>
     <col min="180" max="180" width="17.6640625" customWidth="1"/>
-    <col min="181" max="1024" width="9.33203125" style="2"/>
+    <col min="181" max="1026" width="9.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:188" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:190" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2520,7 +2532,7 @@
       <c r="FU1" s="2"/>
       <c r="FX1" s="2"/>
     </row>
-    <row r="2" spans="1:188" ht="60" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:190" ht="60" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -3082,8 +3094,14 @@
       <c r="GE2" s="18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:188" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="GF2" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="GG2" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:190" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
         <v>15</v>
       </c>
@@ -3643,8 +3661,14 @@
       <c r="GE3" s="36" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="4" spans="1:188" s="43" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="GF3" s="36" t="s">
+        <v>503</v>
+      </c>
+      <c r="GG3" s="36" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="4" spans="1:190" s="43" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="37" t="s">
         <v>151</v>
       </c>
@@ -4206,9 +4230,15 @@
       <c r="GE4" s="38" t="s">
         <v>335</v>
       </c>
-      <c r="GF4" s="2"/>
-    </row>
-    <row r="5" spans="1:188" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="GF4" s="38" t="s">
+        <v>501</v>
+      </c>
+      <c r="GG4" s="38" t="s">
+        <v>502</v>
+      </c>
+      <c r="GH4" s="2"/>
+    </row>
+    <row r="5" spans="1:190" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="44" t="s">
         <v>336</v>
       </c>
@@ -4770,13 +4800,19 @@
       <c r="GE5" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="GF5" s="43"/>
-    </row>
-    <row r="6" spans="1:188" x14ac:dyDescent="0.2">
+      <c r="GF5" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="GG5" s="47" t="s">
+        <v>504</v>
+      </c>
+      <c r="GH5" s="43"/>
+    </row>
+    <row r="6" spans="1:190" x14ac:dyDescent="0.2">
       <c r="BM6" s="51"/>
       <c r="BN6" s="2"/>
     </row>
-    <row r="7" spans="1:188" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:190" x14ac:dyDescent="0.2">
       <c r="DY7" s="2"/>
       <c r="EB7" s="2"/>
       <c r="EH7" s="2"/>
@@ -4796,7 +4832,7 @@
       <c r="FU7" s="2"/>
       <c r="FX7" s="2"/>
     </row>
-    <row r="8" spans="1:188" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:190" x14ac:dyDescent="0.2">
       <c r="DY8" s="2"/>
       <c r="EB8" s="2"/>
       <c r="EH8" s="2"/>
@@ -4816,7 +4852,7 @@
       <c r="FU8" s="2"/>
       <c r="FX8" s="2"/>
     </row>
-    <row r="9" spans="1:188" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:190" x14ac:dyDescent="0.2">
       <c r="DY9" s="2"/>
       <c r="EB9" s="2"/>
       <c r="EH9" s="2"/>
@@ -4836,7 +4872,7 @@
       <c r="FU9" s="2"/>
       <c r="FX9" s="2"/>
     </row>
-    <row r="10" spans="1:188" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:190" x14ac:dyDescent="0.2">
       <c r="DY10" s="2"/>
       <c r="EB10" s="2"/>
       <c r="EH10" s="2"/>
@@ -4856,7 +4892,7 @@
       <c r="FU10" s="2"/>
       <c r="FX10" s="2"/>
     </row>
-    <row r="11" spans="1:188" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:190" x14ac:dyDescent="0.2">
       <c r="DY11" s="2"/>
       <c r="EB11" s="2"/>
       <c r="EH11" s="2"/>
@@ -4876,7 +4912,7 @@
       <c r="FU11" s="2"/>
       <c r="FX11" s="2"/>
     </row>
-    <row r="12" spans="1:188" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:190" x14ac:dyDescent="0.2">
       <c r="DY12" s="2"/>
       <c r="EB12" s="2"/>
       <c r="EH12" s="2"/>
@@ -4896,7 +4932,7 @@
       <c r="FU12" s="2"/>
       <c r="FX12" s="2"/>
     </row>
-    <row r="13" spans="1:188" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:190" x14ac:dyDescent="0.2">
       <c r="DY13" s="2"/>
       <c r="EB13" s="2"/>
       <c r="EH13" s="2"/>
@@ -4916,7 +4952,7 @@
       <c r="FU13" s="2"/>
       <c r="FX13" s="2"/>
     </row>
-    <row r="14" spans="1:188" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:190" x14ac:dyDescent="0.2">
       <c r="DY14" s="2"/>
       <c r="EB14" s="2"/>
       <c r="EH14" s="2"/>
@@ -4936,7 +4972,7 @@
       <c r="FU14" s="2"/>
       <c r="FX14" s="2"/>
     </row>
-    <row r="15" spans="1:188" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:190" x14ac:dyDescent="0.2">
       <c r="DY15" s="2"/>
       <c r="EB15" s="2"/>
       <c r="EH15" s="2"/>
@@ -4956,7 +4992,7 @@
       <c r="FU15" s="2"/>
       <c r="FX15" s="2"/>
     </row>
-    <row r="16" spans="1:188" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:190" x14ac:dyDescent="0.2">
       <c r="DY16" s="2"/>
       <c r="EB16" s="2"/>
       <c r="EH16" s="2"/>
@@ -24757,7 +24793,7 @@
       <c r="FX1005" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="10">
+  <dataValidations disablePrompts="1" count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I6:I1005" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Class,Collection,File,Fonds,Item,Other Level,Record Group,Series,Sub-Fonds,Sub-Group,Sub-Series"</formula1>
       <formula2>0</formula2>
@@ -24790,7 +24826,7 @@
       <formula1>"Creator,Source,Subject"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU6:BU7 CF6 BU8:BU1005" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CF6 BU6:BU1005" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>"MD5,SHA-1,SHA-256,SHA-384,SHA-512"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/frontend/public/bulk_import_templates/bulk_import_template.xlsx
+++ b/frontend/public/bulk_import_templates/bulk_import_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zeffmorgan/src/lyrasis/archivesspace/frontend/public/bulk_import_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95EC3F3-3BEC-0B42-BF65-4C58D83A38D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F8A5BC-475F-9642-9BC6-1B5C95CE886A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34560" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="514">
   <si>
     <t>This is the template for importing archival objects using the bulk_import ("Load SpreadSheet").  You may replace this line with something of your choosing after you've copied the file for your use.</t>
   </si>
@@ -1495,9 +1495,6 @@
   </si>
   <si>
     <t>Ref_ids will be generated for Archival Objects and Digital Objects created with this process.</t>
-  </si>
-  <si>
-    <t>Date Era and Calendar will be set to blank during import.</t>
   </si>
   <si>
     <t xml:space="preserve">barcode will not be added to an existing top container. </t>
@@ -2630,28 +2627,28 @@
         <v>5</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="X2" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="Y2" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AB2" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AC2" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AD2" s="10" t="s">
         <v>6</v>
@@ -3227,10 +3224,10 @@
         <v>39</v>
       </c>
       <c r="AB3" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="AC3" s="25" t="s">
         <v>500</v>
-      </c>
-      <c r="AC3" s="25" t="s">
-        <v>501</v>
       </c>
       <c r="AD3" s="24" t="s">
         <v>34</v>
@@ -3251,10 +3248,10 @@
         <v>39</v>
       </c>
       <c r="AJ3" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="AK3" s="25" t="s">
         <v>500</v>
-      </c>
-      <c r="AK3" s="25" t="s">
-        <v>501</v>
       </c>
       <c r="AL3" s="27" t="s">
         <v>40</v>
@@ -3719,10 +3716,10 @@
         <v>149</v>
       </c>
       <c r="GJ3" s="36" t="s">
+        <v>510</v>
+      </c>
+      <c r="GK3" s="36" t="s">
         <v>511</v>
-      </c>
-      <c r="GK3" s="36" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:193" s="43" customFormat="1" ht="56.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3790,28 +3787,28 @@
         <v>170</v>
       </c>
       <c r="V4" s="38" t="s">
+        <v>493</v>
+      </c>
+      <c r="W4" s="39" t="s">
         <v>494</v>
       </c>
-      <c r="W4" s="39" t="s">
+      <c r="X4" s="39" t="s">
         <v>495</v>
       </c>
-      <c r="X4" s="39" t="s">
+      <c r="Y4" s="38" t="s">
         <v>496</v>
       </c>
-      <c r="Y4" s="38" t="s">
+      <c r="Z4" s="39" t="s">
         <v>497</v>
       </c>
-      <c r="Z4" s="39" t="s">
+      <c r="AA4" s="38" t="s">
         <v>498</v>
       </c>
-      <c r="AA4" s="38" t="s">
-        <v>499</v>
-      </c>
       <c r="AB4" s="39" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AC4" s="39" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AD4" s="38" t="s">
         <v>171</v>
@@ -3832,10 +3829,10 @@
         <v>176</v>
       </c>
       <c r="AJ4" s="39" t="s">
+        <v>506</v>
+      </c>
+      <c r="AK4" s="39" t="s">
         <v>507</v>
-      </c>
-      <c r="AK4" s="39" t="s">
-        <v>508</v>
       </c>
       <c r="AL4" s="38" t="s">
         <v>177</v>
@@ -4162,7 +4159,7 @@
         <v>283</v>
       </c>
       <c r="EP4" s="38" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="EQ4" s="40" t="s">
         <v>284</v>
@@ -4300,10 +4297,10 @@
         <v>328</v>
       </c>
       <c r="GJ4" s="38" t="s">
+        <v>512</v>
+      </c>
+      <c r="GK4" s="38" t="s">
         <v>513</v>
-      </c>
-      <c r="GK4" s="38" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="5" spans="1:193" ht="57" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4389,10 +4386,10 @@
         <v>351</v>
       </c>
       <c r="AB5" s="50" t="s">
+        <v>502</v>
+      </c>
+      <c r="AC5" s="50" t="s">
         <v>503</v>
-      </c>
-      <c r="AC5" s="50" t="s">
-        <v>504</v>
       </c>
       <c r="AD5" s="47" t="s">
         <v>352</v>
@@ -4413,10 +4410,10 @@
         <v>357</v>
       </c>
       <c r="AJ5" s="50" t="s">
+        <v>508</v>
+      </c>
+      <c r="AK5" s="50" t="s">
         <v>509</v>
-      </c>
-      <c r="AK5" s="50" t="s">
-        <v>510</v>
       </c>
       <c r="AL5" s="47" t="s">
         <v>358</v>
@@ -4743,7 +4740,7 @@
         <v>451</v>
       </c>
       <c r="EP5" s="47" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="EQ5" s="47" t="s">
         <v>452</v>
@@ -4881,10 +4878,10 @@
         <v>149</v>
       </c>
       <c r="GJ5" s="47" t="s">
+        <v>510</v>
+      </c>
+      <c r="GK5" s="47" t="s">
         <v>511</v>
-      </c>
-      <c r="GK5" s="47" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="6" spans="1:193" ht="16" thickTop="1" x14ac:dyDescent="0.2">
@@ -24921,7 +24918,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="128.33203125" customWidth="1"/>
@@ -24960,11 +24957,6 @@
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>487</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -24983,17 +24975,17 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
